--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729078</v>
+        <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550606</v>
+        <v>550566</v>
       </c>
       <c r="R7" t="n">
-        <v>6998484</v>
+        <v>6998483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729080</v>
+        <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>99132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550566</v>
+        <v>550606</v>
       </c>
       <c r="R8" t="n">
-        <v>6998483</v>
+        <v>6998484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133729069</v>
+        <v>133729082</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550550</v>
+        <v>550585</v>
       </c>
       <c r="R10" t="n">
-        <v>6998792</v>
+        <v>6998486</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133729082</v>
+        <v>133729069</v>
       </c>
       <c r="B11" t="n">
-        <v>99152</v>
+        <v>99132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550585</v>
+        <v>550550</v>
       </c>
       <c r="R11" t="n">
-        <v>6998486</v>
+        <v>6998792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99152</v>
+        <v>99132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R14" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729080</v>
+        <v>133729078</v>
       </c>
       <c r="B7" t="n">
-        <v>80439</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550566</v>
+        <v>550606</v>
       </c>
       <c r="R7" t="n">
-        <v>6998483</v>
+        <v>6998484</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729078</v>
+        <v>133729080</v>
       </c>
       <c r="B8" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550606</v>
+        <v>550566</v>
       </c>
       <c r="R8" t="n">
-        <v>6998484</v>
+        <v>6998483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729078</v>
+        <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550606</v>
+        <v>550566</v>
       </c>
       <c r="R7" t="n">
-        <v>6998484</v>
+        <v>6998483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729080</v>
+        <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550566</v>
+        <v>550606</v>
       </c>
       <c r="R8" t="n">
-        <v>6998483</v>
+        <v>6998484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133729082</v>
+        <v>133729069</v>
       </c>
       <c r="B10" t="n">
-        <v>99154</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550585</v>
+        <v>550550</v>
       </c>
       <c r="R10" t="n">
-        <v>6998486</v>
+        <v>6998792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133729069</v>
+        <v>133729082</v>
       </c>
       <c r="B11" t="n">
-        <v>99132</v>
+        <v>99162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550550</v>
+        <v>550585</v>
       </c>
       <c r="R11" t="n">
-        <v>6998792</v>
+        <v>6998486</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B13" t="n">
-        <v>99132</v>
+        <v>99162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R13" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B14" t="n">
-        <v>99154</v>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R14" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99162</v>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99140</v>
+        <v>99162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R14" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80467</v>
+        <v>80481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>133729076</v>
       </c>
       <c r="B6" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133729069</v>
+        <v>133729082</v>
       </c>
       <c r="B10" t="n">
-        <v>99140</v>
+        <v>99190</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550550</v>
+        <v>550585</v>
       </c>
       <c r="R10" t="n">
-        <v>6998792</v>
+        <v>6998486</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133729082</v>
+        <v>133729069</v>
       </c>
       <c r="B11" t="n">
-        <v>99162</v>
+        <v>99168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550585</v>
+        <v>550550</v>
       </c>
       <c r="R11" t="n">
-        <v>6998486</v>
+        <v>6998792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99162</v>
+        <v>99190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B13" t="n">
-        <v>99168</v>
+        <v>99190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R13" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B14" t="n">
-        <v>99190</v>
+        <v>99168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R14" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>133729076</v>
       </c>
       <c r="B6" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>133729082</v>
       </c>
       <c r="B10" t="n">
-        <v>99190</v>
+        <v>99200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>133729069</v>
       </c>
       <c r="B11" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133729070</v>
       </c>
       <c r="B13" t="n">
-        <v>99190</v>
+        <v>99200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133729083</v>
       </c>
       <c r="B14" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99200</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R14" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729080</v>
+        <v>133729078</v>
       </c>
       <c r="B7" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550566</v>
+        <v>550606</v>
       </c>
       <c r="R7" t="n">
-        <v>6998483</v>
+        <v>6998484</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729078</v>
+        <v>133729080</v>
       </c>
       <c r="B8" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550606</v>
+        <v>550566</v>
       </c>
       <c r="R8" t="n">
-        <v>6998484</v>
+        <v>6998483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R13" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B14" t="n">
-        <v>99200</v>
+        <v>99178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R14" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729078</v>
+        <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550606</v>
+        <v>550566</v>
       </c>
       <c r="R7" t="n">
-        <v>6998484</v>
+        <v>6998483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729080</v>
+        <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550566</v>
+        <v>550606</v>
       </c>
       <c r="R8" t="n">
-        <v>6998483</v>
+        <v>6998484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99200</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729083</v>
+        <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550585</v>
+        <v>550604</v>
       </c>
       <c r="R14" t="n">
-        <v>6998486</v>
+        <v>6998745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>133729082</v>
       </c>
       <c r="B10" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>133729069</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729084</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133729068</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133729071</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>133729080</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>133729078</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>133729085</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>133729082</v>
       </c>
       <c r="B10" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>133729069</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133729067</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133729083</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>133729070</v>
       </c>
       <c r="B14" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133729084</v>
+        <v>133729096</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550723</v>
+        <v>550668</v>
       </c>
       <c r="R2" t="n">
-        <v>6998504</v>
+        <v>6998719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133729068</v>
+        <v>133729094</v>
       </c>
       <c r="B3" t="n">
-        <v>99188</v>
+        <v>92199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550587</v>
+        <v>550539</v>
       </c>
       <c r="R3" t="n">
-        <v>6998825</v>
+        <v>6998730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133729071</v>
+        <v>133729080</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550604</v>
+        <v>550566</v>
       </c>
       <c r="R4" t="n">
-        <v>6998745</v>
+        <v>6998483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>133729081</v>
       </c>
       <c r="B5" t="n">
-        <v>80485</v>
+        <v>80492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729080</v>
+        <v>133729092</v>
       </c>
       <c r="B7" t="n">
-        <v>80481</v>
+        <v>108274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220102</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550566</v>
+        <v>550539</v>
       </c>
       <c r="R7" t="n">
-        <v>6998483</v>
+        <v>6998730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729078</v>
+        <v>133729067</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550606</v>
+        <v>550552</v>
       </c>
       <c r="R8" t="n">
-        <v>6998484</v>
+        <v>6998820</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133729085</v>
+        <v>133729068</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,20 +1383,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550735</v>
+        <v>550587</v>
       </c>
       <c r="R9" t="n">
-        <v>6998530</v>
+        <v>6998825</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,18 +1427,12 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på mossig låga över vattnet i dråg</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1461,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133729082</v>
+        <v>133729069</v>
       </c>
       <c r="B10" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550585</v>
+        <v>550550</v>
       </c>
       <c r="R10" t="n">
-        <v>6998486</v>
+        <v>6998792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133729069</v>
+        <v>133729071</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550550</v>
+        <v>550604</v>
       </c>
       <c r="R11" t="n">
-        <v>6998792</v>
+        <v>6998745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133729067</v>
+        <v>133729072</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550552</v>
+        <v>550546</v>
       </c>
       <c r="R12" t="n">
-        <v>6998820</v>
+        <v>6998750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729083</v>
+        <v>133729078</v>
       </c>
       <c r="B13" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550606</v>
       </c>
       <c r="R13" t="n">
-        <v>6998486</v>
+        <v>6998484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729070</v>
+        <v>133729083</v>
       </c>
       <c r="B14" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550604</v>
+        <v>550585</v>
       </c>
       <c r="R14" t="n">
-        <v>6998745</v>
+        <v>6998486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1943,6 +1933,695 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133729084</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550723</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6998504</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133729085</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550735</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6998530</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på mossig låga över vattnet i dråg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133729070</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550604</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6998745</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133729082</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550585</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6998486</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133729087</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550719</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6998593</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133729091</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6998730</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133729093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6998730</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133729092</v>
+        <v>134654411</v>
       </c>
       <c r="B7" t="n">
-        <v>108274</v>
+        <v>99197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220102</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550539</v>
+        <v>550548</v>
       </c>
       <c r="R7" t="n">
-        <v>6998730</v>
+        <v>6998715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,57 +1245,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133729067</v>
+        <v>134654412</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550552</v>
+        <v>550545</v>
       </c>
       <c r="R8" t="n">
-        <v>6998820</v>
+        <v>6998708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133729068</v>
+        <v>133729092</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550587</v>
+        <v>550539</v>
       </c>
       <c r="R9" t="n">
-        <v>6998825</v>
+        <v>6998730</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133729069</v>
+        <v>133729067</v>
       </c>
       <c r="B10" t="n">
         <v>99195</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550550</v>
+        <v>550552</v>
       </c>
       <c r="R10" t="n">
-        <v>6998792</v>
+        <v>6998820</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133729071</v>
+        <v>133729068</v>
       </c>
       <c r="B11" t="n">
         <v>99195</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550604</v>
+        <v>550587</v>
       </c>
       <c r="R11" t="n">
-        <v>6998745</v>
+        <v>6998825</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133729072</v>
+        <v>133729069</v>
       </c>
       <c r="B12" t="n">
         <v>99195</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550546</v>
+        <v>550550</v>
       </c>
       <c r="R12" t="n">
-        <v>6998750</v>
+        <v>6998792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133729078</v>
+        <v>133729071</v>
       </c>
       <c r="B13" t="n">
         <v>99195</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550606</v>
+        <v>550604</v>
       </c>
       <c r="R13" t="n">
-        <v>6998484</v>
+        <v>6998745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133729083</v>
+        <v>133729072</v>
       </c>
       <c r="B14" t="n">
         <v>99195</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550585</v>
+        <v>550546</v>
       </c>
       <c r="R14" t="n">
-        <v>6998486</v>
+        <v>6998750</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133729084</v>
+        <v>133729078</v>
       </c>
       <c r="B15" t="n">
         <v>99195</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550723</v>
+        <v>550606</v>
       </c>
       <c r="R15" t="n">
-        <v>6998504</v>
+        <v>6998484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133729085</v>
+        <v>133729083</v>
       </c>
       <c r="B16" t="n">
         <v>99195</v>
@@ -2062,20 +2062,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550735</v>
+        <v>550585</v>
       </c>
       <c r="R16" t="n">
-        <v>6998530</v>
+        <v>6998486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,18 +2106,12 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>på mossig låga över vattnet i dråg</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2140,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133729070</v>
+        <v>133729084</v>
       </c>
       <c r="B17" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550604</v>
+        <v>550723</v>
       </c>
       <c r="R17" t="n">
-        <v>6998745</v>
+        <v>6998504</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,45 +2227,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133729082</v>
+        <v>133729085</v>
       </c>
       <c r="B18" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550585</v>
+        <v>550735</v>
       </c>
       <c r="R18" t="n">
-        <v>6998486</v>
+        <v>6998530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2310,12 +2304,18 @@
           <t>2026-05-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>på mossig låga över vattnet i dråg</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2334,45 +2334,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133729087</v>
+        <v>134654425</v>
       </c>
       <c r="B19" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550719</v>
+        <v>550509</v>
       </c>
       <c r="R19" t="n">
-        <v>6998593</v>
+        <v>6998764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133729091</v>
+        <v>133729070</v>
       </c>
       <c r="B20" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550539</v>
+        <v>550604</v>
       </c>
       <c r="R20" t="n">
-        <v>6998730</v>
+        <v>6998745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133729093</v>
+        <v>133729082</v>
       </c>
       <c r="B21" t="n">
-        <v>99504</v>
+        <v>99217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222857</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550539</v>
+        <v>550585</v>
       </c>
       <c r="R21" t="n">
-        <v>6998730</v>
+        <v>6998486</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2622,6 +2622,394 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133729087</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550719</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6998593</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134654426</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550513</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6998765</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133729091</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6998730</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133729093</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6998730</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20574-2025 artfynd.xlsx
+++ b/artfynd/A 20574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729096</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729076</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654411</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729092</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729067</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729068</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729069</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729071</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729072</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729078</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729083</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729084</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729085</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654425</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729070</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729082</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729087</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654426</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729091</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,8 +3130,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>